--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -3675,7 +3675,7 @@
         <v>136042898</v>
       </c>
       <c r="B30" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136042903</v>
       </c>
       <c r="B31" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -3675,7 +3675,7 @@
         <v>136042898</v>
       </c>
       <c r="B30" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>136042903</v>
       </c>
       <c r="B31" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135431666</v>
+        <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>80590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490127</v>
+        <v>489884</v>
       </c>
       <c r="R2" t="n">
-        <v>6848356</v>
+        <v>6847914</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +784,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431666</t>
+          <t>https://artportalen.se/Sighting/136759769</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135430496</v>
+        <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>79200</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +812,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490087</v>
+        <v>489769</v>
       </c>
       <c r="R3" t="n">
-        <v>6848091</v>
+        <v>6848097</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +870,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +905,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430496</t>
+          <t>https://artportalen.se/Sighting/136759883</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136042902</v>
+        <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>79231</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -923,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489554</v>
+        <v>489818</v>
       </c>
       <c r="R4" t="n">
-        <v>6848182</v>
+        <v>6848054</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +991,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -989,58 +1037,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042902</t>
+          <t>https://artportalen.se/Sighting/136759796</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136042905</v>
+        <v>135431666</v>
       </c>
       <c r="B5" t="n">
-        <v>79231</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rullbo, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489724</v>
+        <v>490127</v>
       </c>
       <c r="R5" t="n">
-        <v>6848320</v>
+        <v>6848356</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,17 +1108,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,27 +1128,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042905</t>
+          <t>https://artportalen.se/Sighting/135431666</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112181718</v>
+        <v>135430496</v>
       </c>
       <c r="B6" t="n">
-        <v>80432</v>
+        <v>79200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,41 +1156,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rullbo, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489869</v>
+        <v>490087</v>
       </c>
       <c r="R6" t="n">
-        <v>6847851</v>
+        <v>6848091</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,17 +1210,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,27 +1230,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112181718</t>
+          <t>https://artportalen.se/Sighting/135430496</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136042901</v>
+        <v>136042902</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>79231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,21 +1258,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1256,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489542</v>
+        <v>489554</v>
       </c>
       <c r="R7" t="n">
-        <v>6848201</v>
+        <v>6848182</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1322,63 +1352,58 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042901</t>
+          <t>https://artportalen.se/Sighting/136042902</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135428817</v>
+        <v>136042905</v>
       </c>
       <c r="B8" t="n">
-        <v>57169</v>
+        <v>79231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>1K</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489686</v>
+        <v>489724</v>
       </c>
       <c r="R8" t="n">
-        <v>6848174</v>
+        <v>6848320</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,12 +1427,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,80 +1452,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135428817</t>
+          <t>https://artportalen.se/Sighting/136042905</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135429631</v>
+        <v>112181718</v>
       </c>
       <c r="B9" t="n">
-        <v>57169</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489885</v>
+        <v>489869</v>
       </c>
       <c r="R9" t="n">
-        <v>6848133</v>
+        <v>6847851</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,12 +1538,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,80 +1563,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135429631</t>
+          <t>https://artportalen.se/Sighting/112181718</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135430122</v>
+        <v>136042901</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>80589</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490038</v>
+        <v>489542</v>
       </c>
       <c r="R10" t="n">
-        <v>6848065</v>
+        <v>6848201</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,12 +1649,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,80 +1674,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430122</t>
+          <t>https://artportalen.se/Sighting/136042901</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135431705</v>
+        <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>80589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490106</v>
+        <v>489886</v>
       </c>
       <c r="R11" t="n">
-        <v>6848374</v>
+        <v>6847916</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,12 +1760,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,64 +1795,59 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431705</t>
+          <t>https://artportalen.se/Sighting/136759803</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135429557</v>
+        <v>135428817</v>
       </c>
       <c r="B12" t="n">
-        <v>58417</v>
+        <v>57169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1839,13 +1856,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489799</v>
+        <v>489686</v>
       </c>
       <c r="R12" t="n">
-        <v>6848087</v>
+        <v>6848174</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,11 +1902,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1905,16 +1917,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135429557</t>
+          <t>https://artportalen.se/Sighting/135428817</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135429817</v>
+        <v>135429631</v>
       </c>
       <c r="B13" t="n">
-        <v>99210</v>
+        <v>57169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,37 +1934,52 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489942</v>
+        <v>489885</v>
       </c>
       <c r="R13" t="n">
-        <v>6848149</v>
+        <v>6848133</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,16 +2034,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135429817</t>
+          <t>https://artportalen.se/Sighting/135429631</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135430711</v>
+        <v>135430122</v>
       </c>
       <c r="B14" t="n">
-        <v>99210</v>
+        <v>57169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,37 +2051,52 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489990</v>
+        <v>490038</v>
       </c>
       <c r="R14" t="n">
-        <v>6848129</v>
+        <v>6848065</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2109,16 +2151,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430711</t>
+          <t>https://artportalen.se/Sighting/135430122</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135430823</v>
+        <v>135431705</v>
       </c>
       <c r="B15" t="n">
-        <v>99210</v>
+        <v>57169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,37 +2168,52 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490043</v>
+        <v>490106</v>
       </c>
       <c r="R15" t="n">
-        <v>6848215</v>
+        <v>6848374</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,54 +2268,68 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430823</t>
+          <t>https://artportalen.se/Sighting/135431705</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135431271</v>
+        <v>135429557</v>
       </c>
       <c r="B16" t="n">
-        <v>99328</v>
+        <v>58417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>103001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490154</v>
+        <v>489799</v>
       </c>
       <c r="R16" t="n">
-        <v>6848240</v>
+        <v>6848087</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2298,6 +2369,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2313,16 +2389,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431271</t>
+          <t>https://artportalen.se/Sighting/135429557</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135431283</v>
+        <v>135429817</v>
       </c>
       <c r="B17" t="n">
-        <v>99328</v>
+        <v>99210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2406,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490151</v>
+        <v>489942</v>
       </c>
       <c r="R17" t="n">
-        <v>6848231</v>
+        <v>6848149</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,60 +2491,51 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431283</t>
+          <t>https://artportalen.se/Sighting/135429817</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135429232</v>
+        <v>135430711</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489785</v>
+        <v>489990</v>
       </c>
       <c r="R18" t="n">
-        <v>6848000</v>
+        <v>6848129</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2526,38 +2593,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135429232</t>
+          <t>https://artportalen.se/Sighting/135430711</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135430208</v>
+        <v>135430823</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2567,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490064</v>
+        <v>490043</v>
       </c>
       <c r="R19" t="n">
-        <v>6848121</v>
+        <v>6848215</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,38 +2695,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430208</t>
+          <t>https://artportalen.se/Sighting/135430823</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135430251</v>
+        <v>135431271</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2669,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490055</v>
+        <v>490154</v>
       </c>
       <c r="R20" t="n">
-        <v>6848127</v>
+        <v>6848240</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,38 +2797,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430251</t>
+          <t>https://artportalen.se/Sighting/135431271</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135430270</v>
+        <v>135431283</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490037</v>
+        <v>490151</v>
       </c>
       <c r="R21" t="n">
-        <v>6848115</v>
+        <v>6848231</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2832,13 +2899,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430270</t>
+          <t>https://artportalen.se/Sighting/135431283</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135430474</v>
+        <v>135429232</v>
       </c>
       <c r="B22" t="n">
         <v>99293</v>
@@ -2866,17 +2933,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490087</v>
+        <v>489785</v>
       </c>
       <c r="R22" t="n">
-        <v>6848100</v>
+        <v>6848000</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,13 +3010,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430474</t>
+          <t>https://artportalen.se/Sighting/135429232</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135430855</v>
+        <v>135430208</v>
       </c>
       <c r="B23" t="n">
         <v>99293</v>
@@ -2975,10 +3051,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490054</v>
+        <v>490064</v>
       </c>
       <c r="R23" t="n">
-        <v>6848206</v>
+        <v>6848121</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,13 +3112,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430855</t>
+          <t>https://artportalen.se/Sighting/135430208</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135431313</v>
+        <v>135430251</v>
       </c>
       <c r="B24" t="n">
         <v>99293</v>
@@ -3077,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490147</v>
+        <v>490055</v>
       </c>
       <c r="R24" t="n">
-        <v>6848240</v>
+        <v>6848127</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,13 +3214,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431313</t>
+          <t>https://artportalen.se/Sighting/135430251</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135431477</v>
+        <v>135430270</v>
       </c>
       <c r="B25" t="n">
         <v>99293</v>
@@ -3172,26 +3248,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490169</v>
+        <v>490037</v>
       </c>
       <c r="R25" t="n">
-        <v>6848351</v>
+        <v>6848115</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,13 +3316,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431477</t>
+          <t>https://artportalen.se/Sighting/135430270</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135431652</v>
+        <v>135430474</v>
       </c>
       <c r="B26" t="n">
         <v>99293</v>
@@ -3286,14 +3353,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490121</v>
+        <v>490087</v>
       </c>
       <c r="R26" t="n">
-        <v>6848345</v>
+        <v>6848100</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,13 +3418,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431652</t>
+          <t>https://artportalen.se/Sighting/135430474</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135431942</v>
+        <v>135430855</v>
       </c>
       <c r="B27" t="n">
         <v>99293</v>
@@ -3388,14 +3455,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490110</v>
+        <v>490054</v>
       </c>
       <c r="R27" t="n">
-        <v>6848436</v>
+        <v>6848206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3453,13 +3520,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135431942</t>
+          <t>https://artportalen.se/Sighting/135430855</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135432247</v>
+        <v>135431313</v>
       </c>
       <c r="B28" t="n">
         <v>99293</v>
@@ -3490,14 +3557,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490053</v>
+        <v>490147</v>
       </c>
       <c r="R28" t="n">
-        <v>6848327</v>
+        <v>6848240</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3555,13 +3622,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135432247</t>
+          <t>https://artportalen.se/Sighting/135431313</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135432573</v>
+        <v>135431477</v>
       </c>
       <c r="B29" t="n">
         <v>99293</v>
@@ -3591,7 +3658,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3605,10 +3672,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489761</v>
+        <v>490169</v>
       </c>
       <c r="R29" t="n">
-        <v>6848218</v>
+        <v>6848351</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3666,58 +3733,54 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135432573</t>
+          <t>https://artportalen.se/Sighting/135431477</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136042898</v>
+        <v>135431652</v>
       </c>
       <c r="B30" t="n">
-        <v>98214</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rullbo, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489802</v>
+        <v>490121</v>
       </c>
       <c r="R30" t="n">
-        <v>6848139</v>
+        <v>6848345</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3741,17 +3804,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3766,66 +3824,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042898</t>
+          <t>https://artportalen.se/Sighting/135431652</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136042903</v>
+        <v>135431942</v>
       </c>
       <c r="B31" t="n">
-        <v>98214</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rullbo, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489768</v>
+        <v>490110</v>
       </c>
       <c r="R31" t="n">
-        <v>6848103</v>
+        <v>6848436</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,17 +3906,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,62 +3926,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042903</t>
+          <t>https://artportalen.se/Sighting/135431942</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135430638</v>
+        <v>135432247</v>
       </c>
       <c r="B32" t="n">
-        <v>99211</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Vålbergsmyran, Vålbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490014</v>
+        <v>490053</v>
       </c>
       <c r="R32" t="n">
-        <v>6848138</v>
+        <v>6848327</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,51 +4039,60 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430638</t>
+          <t>https://artportalen.se/Sighting/135432247</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135430729</v>
+        <v>135432573</v>
       </c>
       <c r="B33" t="n">
-        <v>99211</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489990</v>
+        <v>489761</v>
       </c>
       <c r="R33" t="n">
-        <v>6848135</v>
+        <v>6848218</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4092,16 +4150,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135430729</t>
+          <t>https://artportalen.se/Sighting/135432573</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135430884</v>
+        <v>136042898</v>
       </c>
       <c r="B34" t="n">
-        <v>99211</v>
+        <v>98214</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4109,37 +4167,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223591</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Rullbo, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490064</v>
+        <v>489802</v>
       </c>
       <c r="R34" t="n">
-        <v>6848204</v>
+        <v>6848139</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4163,12 +4225,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4183,16 +4250,554 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042898</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136042903</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98214</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rullbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>489768</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6848103</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042903</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136759781</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98214</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Rullbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>489797</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6848307</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759781</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135430638</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99211</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>490014</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6848138</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430638</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135430729</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99211</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>489990</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6848135</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430729</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135430884</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99211</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>490064</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6848204</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135430884</t>
         </is>
@@ -4233,6 +4838,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759769</v>
       </c>
       <c r="B2" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136759803</v>
       </c>
       <c r="B11" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30010-2026 artfynd.xlsx
+++ b/artfynd/A 30010-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136759883</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136759796</v>
       </c>
       <c r="B4" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136759781</v>
       </c>
       <c r="B36" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
